--- a/DCZ/touch_rect_log_20260604_161308.xlsx
+++ b/DCZ/touch_rect_log_20260604_161308.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\logs\294\DCZ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EtoHayato\Desktop\git_repository\294\DCZ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DD43BF0-D772-46BB-BEBC-7EF22E574E54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8E79502-49A1-4691-9036-98A8BB4C7AA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="105" windowWidth="25785" windowHeight="15375" activeTab="1" xr2:uid="{456775EC-F742-4D40-810C-3EF4371D9F7D}"/>
+    <workbookView xWindow="17850" yWindow="1560" windowWidth="25455" windowHeight="14670" activeTab="1" xr2:uid="{456775EC-F742-4D40-810C-3EF4371D9F7D}"/>
   </bookViews>
   <sheets>
     <sheet name="touch_rect_log_20260604_161308" sheetId="1" r:id="rId1"/>
@@ -4109,7 +4109,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="179" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+    <numFmt numFmtId="176" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
   <fonts count="19" x14ac:knownFonts="1">
     <font>
@@ -4701,7 +4701,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -4797,7 +4797,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US" altLang="ja-JP"/>
-              <a:t>6/4 DCZ 0.1 ug/kg</a:t>
+              <a:t>6/4 DCZ 1 ug/kg</a:t>
             </a:r>
             <a:endParaRPr lang="ja-JP" altLang="en-US"/>
           </a:p>
@@ -4828,7 +4828,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="ja-JP"/>
+          <a:endParaRPr lang="ja-JP" altLang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -6537,16 +6537,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>42862</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>338136</xdr:colOff>
       <xdr:row>285</xdr:row>
-      <xdr:rowOff>23812</xdr:rowOff>
+      <xdr:rowOff>42862</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>500062</xdr:colOff>
-      <xdr:row>296</xdr:row>
-      <xdr:rowOff>147637</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>476250</xdr:colOff>
+      <xdr:row>308</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>

--- a/DCZ/touch_rect_log_20260604_161308.xlsx
+++ b/DCZ/touch_rect_log_20260604_161308.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\logs\294\DCZ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DD43BF0-D772-46BB-BEBC-7EF22E574E54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8AF8BDF-0398-4CC4-B602-9F96458D50A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="105" windowWidth="25785" windowHeight="15375" activeTab="1" xr2:uid="{456775EC-F742-4D40-810C-3EF4371D9F7D}"/>
   </bookViews>
@@ -6537,16 +6537,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>42862</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>504825</xdr:colOff>
       <xdr:row>285</xdr:row>
-      <xdr:rowOff>23812</xdr:rowOff>
+      <xdr:rowOff>23811</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>500062</xdr:colOff>
-      <xdr:row>296</xdr:row>
-      <xdr:rowOff>147637</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>676275</xdr:colOff>
+      <xdr:row>304</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
